--- a/artfynd/A 22907-2023 artfynd.xlsx
+++ b/artfynd/A 22907-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2298,6 +2298,131 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>113530472</v>
+      </c>
+      <c r="B15" t="n">
+        <v>108183</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Källdalen (svinrot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>558248</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6629287</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>U-Sur-0573</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>X: (5) fullt utv blad, A: 072/870 (5) 1 ex blomning</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Greta Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22907-2023 artfynd.xlsx
+++ b/artfynd/A 22907-2023 artfynd.xlsx
@@ -2303,7 +2303,7 @@
         <v>113530472</v>
       </c>
       <c r="B15" t="n">
-        <v>108183</v>
+        <v>108187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2023 artfynd.xlsx
+++ b/artfynd/A 22907-2023 artfynd.xlsx
@@ -2303,7 +2303,7 @@
         <v>113530472</v>
       </c>
       <c r="B15" t="n">
-        <v>108187</v>
+        <v>108193</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2023 artfynd.xlsx
+++ b/artfynd/A 22907-2023 artfynd.xlsx
@@ -2303,7 +2303,7 @@
         <v>113530472</v>
       </c>
       <c r="B15" t="n">
-        <v>108193</v>
+        <v>108200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2023 artfynd.xlsx
+++ b/artfynd/A 22907-2023 artfynd.xlsx
@@ -2303,7 +2303,7 @@
         <v>113530472</v>
       </c>
       <c r="B15" t="n">
-        <v>108200</v>
+        <v>108205</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2023 artfynd.xlsx
+++ b/artfynd/A 22907-2023 artfynd.xlsx
@@ -2303,7 +2303,7 @@
         <v>113530472</v>
       </c>
       <c r="B15" t="n">
-        <v>108205</v>
+        <v>108235</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2023 artfynd.xlsx
+++ b/artfynd/A 22907-2023 artfynd.xlsx
@@ -2303,7 +2303,7 @@
         <v>113530472</v>
       </c>
       <c r="B15" t="n">
-        <v>108235</v>
+        <v>108249</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 22907-2023 artfynd.xlsx
+++ b/artfynd/A 22907-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22907-2023 artfynd.xlsx
+++ b/artfynd/A 22907-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2298,131 +2298,6 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>113530472</v>
-      </c>
-      <c r="B15" t="n">
-        <v>108510</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>220299</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Svinrot</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Källdalen (svinrot), Vstm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>558248</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6629287</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>U-Sur-0573</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>X: (5) fullt utv blad, A: 072/870 (5) 1 ex blomning</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Bo Eriksson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Sören Larsson, Greta Larsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22907-2023 artfynd.xlsx
+++ b/artfynd/A 22907-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66300586</v>
+        <v>104866923</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>5321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Källdalen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558238.0796939648</v>
+        <v>558246</v>
       </c>
       <c r="R2" t="n">
-        <v>6629248.068933387</v>
+        <v>6629191</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-06-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-06-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,12 +757,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Vägslänt, dikesren</t>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Asphögstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>77111620</v>
+        <v>81914623</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,38 +797,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granramen V, Vstm</t>
+          <t>Källdalen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558495.9970460979</v>
+        <v>558329</v>
       </c>
       <c r="R3" t="n">
-        <v>6629167.04819921</v>
+        <v>6629064</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,22 +863,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-04-18</t>
+          <t>2020-01-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-04-18</t>
+          <t>2020-01-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,39 +887,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Blandskog gran, björk, tall</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2984058</v>
+        <v>110683796</v>
       </c>
       <c r="B4" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,37 +916,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219875</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Källdalen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558329.1985270862</v>
+        <v>558153</v>
       </c>
       <c r="R4" t="n">
-        <v>6629064.258449391</v>
+        <v>6629307</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +982,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2010-07-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2010-07-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,11 +998,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Fuktig barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1027,22 +1007,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81914623</v>
+        <v>81801024</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,33 +1025,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1086,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558329.1985270862</v>
+        <v>558315</v>
       </c>
       <c r="R5" t="n">
-        <v>6629064.258449391</v>
+        <v>6628979</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1116,22 +1091,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-01-25</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-01-25</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,64 +1126,67 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Sören Larsson, Greta Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104866653</v>
+        <v>110000343</v>
       </c>
       <c r="B6" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Källdalen, Vstm</t>
+          <t>Källdalen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558219.2158932125</v>
+        <v>558191</v>
       </c>
       <c r="R6" t="n">
-        <v>6629325.792350452</v>
+        <v>6629212</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1232,22 +1210,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,77 +1224,79 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson, Pia Hagfors, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104866923</v>
+        <v>110000350</v>
       </c>
       <c r="B7" t="n">
-        <v>89794</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5321</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Källdalen, Vstm</t>
+          <t>Källdalen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558245.5231793012</v>
+        <v>558156</v>
       </c>
       <c r="R7" t="n">
-        <v>6629191.30629319</v>
+        <v>6629210</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,22 +1323,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lockar även</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,97 +1342,82 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Asphögstubbe</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Sören Larsson, Pia Hagfors, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109203531</v>
+        <v>110000407</v>
       </c>
       <c r="B8" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Källdalen (NO om), Vstm</t>
+          <t>Källdalen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558476.537164674</v>
+        <v>558199</v>
       </c>
       <c r="R8" t="n">
-        <v>6629121.942600886</v>
+        <v>6629247</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1491,27 +1441,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>riklig förekomst intill dike/bäck</t>
+          <t>Häckar i 5 m hög björkstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,27 +1466,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Rehnberg</t>
+          <t>Sören Larsson, Pia Hagfors, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110000322</v>
+        <v>131869489</v>
       </c>
       <c r="B9" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,21 +1489,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1576,13 +1511,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1590,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558258.7390567887</v>
+        <v>558172</v>
       </c>
       <c r="R9" t="n">
-        <v>6629281.110148298</v>
+        <v>6629169</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1620,22 +1555,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,7 +1579,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1656,68 +1590,55 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Bengt Eriksson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110000307</v>
+        <v>2984058</v>
       </c>
       <c r="B10" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>219875</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Källdalen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558247.554691602</v>
+        <v>558329</v>
       </c>
       <c r="R10" t="n">
-        <v>6629286.975165951</v>
+        <v>6629064</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1741,27 +1662,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-07-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Enstaka plantor</t>
+          <t>2010-07-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1770,9 +1676,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Fuktig barrskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1782,22 +1692,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Bengt Eriksson</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110000343</v>
+        <v>94600893</v>
       </c>
       <c r="B11" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1805,46 +1710,50 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Källdalen, Ramnäs sn, Vstm</t>
+          <t>Källdalen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558191.2544514737</v>
+        <v>558244</v>
       </c>
       <c r="R11" t="n">
-        <v>6629211.598016237</v>
+        <v>6629126</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1871,22 +1780,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,33 +1794,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Skogsbilväg</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Bengt Eriksson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110000350</v>
+        <v>110683233</v>
       </c>
       <c r="B12" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,39 +1829,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1969,13 +1861,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558156.5035985712</v>
+        <v>558244</v>
       </c>
       <c r="R12" t="n">
-        <v>6629209.04115126</v>
+        <v>6629176</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1999,27 +1891,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lockar även</t>
+          <t>2023-07-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2028,6 +1905,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2039,22 +1917,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Bengt Eriksson</t>
+          <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110000407</v>
+        <v>66300725</v>
       </c>
       <c r="B13" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,21 +1935,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2084,31 +1957,30 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källdalen, Ramnäs sn, Vstm</t>
+          <t>Källdalen, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558198.7609299219</v>
+        <v>558233</v>
       </c>
       <c r="R13" t="n">
-        <v>6629247.453581648</v>
+        <v>6629342</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2132,27 +2004,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Häckar i 5 m hög björkstubbe</t>
+          <t>2017-06-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2163,31 +2020,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Vägslänt, dikesren</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sören Larsson, Pia Hagfors, Bengt Eriksson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110683233</v>
+        <v>110000307</v>
       </c>
       <c r="B14" t="n">
-        <v>106732</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,16 +2052,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220204</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2227,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558243.7431734009</v>
+        <v>558248</v>
       </c>
       <c r="R14" t="n">
-        <v>6629176.177610914</v>
+        <v>6629287</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2257,22 +2114,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-07-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Enstaka plantor</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2293,10 +2145,662 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
+          <t>Sören Larsson, Pia Hagfors, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>110000322</v>
+      </c>
+      <c r="B15" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Källdalen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>558259</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6629281</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sören Larsson, Pia Hagfors, Bengt Eriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>77111620</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Granramen V, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>558496</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6629167</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2019-04-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2019-04-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Blandskog gran, björk, tall</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>109203531</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Källdalen (NO om), Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>558476</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6629122</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-05-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>riklig förekomst intill dike/bäck</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>104866653</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Källdalen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>558219</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6629326</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-11-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-11-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>66300586</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Källdalen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>558238</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6629248</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2017-06-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2017-06-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Vägslänt, dikesren</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>110683821</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Källdalen, Ramnäs sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>558130</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6629235</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-07-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
           <t>Sören Larsson, Pia Hagfors, Seppo Ormiskangas</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22907-2023 artfynd.xlsx
+++ b/artfynd/A 22907-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104866923</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81914623</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110683796</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81801024</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110000343</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1357,6 +1387,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110000350</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1475,6 +1510,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110000407</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1594,6 +1634,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131869489</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1696,6 +1741,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2984058</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1815,6 +1865,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94600893</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1921,6 +1976,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110683233</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2038,6 +2098,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66300725</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2149,6 +2214,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110000307</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2259,6 +2329,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110000322</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2366,6 +2441,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77111620</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2483,6 +2563,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109203531</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2590,6 +2675,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104866653</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2695,6 +2785,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66300586</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2801,8 +2896,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110683821</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>